--- a/luaran/laporan_akhir/tables/Table6_md_2019_stages.xlsx
+++ b/luaran/laporan_akhir/tables/Table6_md_2019_stages.xlsx
@@ -29,17 +29,29 @@
       <b val="1"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003C7A8C"/>
+        <bgColor rgb="003C7A8C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F4F8"/>
+        <bgColor rgb="00F0F4F8"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -58,25 +70,31 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00000000"/>
+        <color rgb="00CBD5E0"/>
       </left>
       <right style="thin">
-        <color rgb="00000000"/>
+        <color rgb="00CBD5E0"/>
       </right>
       <top style="thin">
-        <color rgb="00000000"/>
+        <color rgb="00CBD5E0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00000000"/>
+        <color rgb="00CBD5E0"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -450,20 +468,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="31" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,290 +484,91 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Params
-(M)</t>
+          <t>Accuracy (%)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Training
-Time (min)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Balanced
-Acc</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Ring
-(n=170)
-Precision</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Ring
-(n=170)
-F1</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Schizont
-(n=286)
-Precision</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Schizont
-(n=286)
-F1</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Trophozoite
-(n=127)
-Precision</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Trophozoite
-(n=127)
-F1</t>
+          <t>Balanced Accuracy (%)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DenseNet121</t>
+          <t>DENSENET121</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>83.53</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0.68</v>
+        <v>82.54000000000001</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>EfficientNet-B0</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>0.74</v>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>EFFICIENTNET-B0</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>86.62</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>85.51000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>EfficientNet-B1</t>
+          <t>EFFICIENTNET-B1</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7.8</v>
+        <v>85.59</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>0.7</v>
+        <v>83.91</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>EfficientNet-B2</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0.67</v>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>EFFICIENTNET-B2</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>84.05</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>81.45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ResNet101</t>
+          <t>RESNET101</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>44.5</v>
+        <v>85.25</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.7</v>
+        <v>83.48</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>ResNet50</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0.67</v>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>RESNET50</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>84.91</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>82.22</v>
       </c>
     </row>
   </sheetData>

--- a/luaran/laporan_akhir/tables/Table6_md_2019_stages.xlsx
+++ b/luaran/laporan_akhir/tables/Table6_md_2019_stages.xlsx
@@ -16,17 +16,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -54,19 +54,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -86,21 +80,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -468,12 +468,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -484,94 +492,308 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Accuracy (%)</t>
+          <t>Parameters (M)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Balanced Accuracy (%)</t>
-        </is>
-      </c>
+          <t>Training Time (min)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Balanced Acc</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ring (n=170)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Schizont (n=286)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Trophozoite (n=127)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>DENSENET121</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>83.53</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>82.54000000000001</v>
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>EFFICIENTNET-B0</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>86.62</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>85.51000000000001</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>DENSENET121</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0.8353</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.8254</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0.8548</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0.8933</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>0.9225</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>0.6475</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>0.6767</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>EFFICIENTNET-B1</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>85.59</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>83.91</v>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>EFFICIENTNET-B0</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>0.8662</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>0.8551</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>0.8641</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>0.8983</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>0.9434</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>0.9074</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>0.7164</v>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>0.7356</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>EFFICIENTNET-B2</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>84.05</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>81.45</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>EFFICIENTNET-B1</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.8559</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.8391</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0.8757</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0.8934</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0.9265</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0.9032</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0.6866</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0.705</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>RESNET101</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>85.25</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>83.48</v>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>EFFICIENTNET-B2</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>0.8405</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>0.8145</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>0.8352000000000001</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0.8636</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0.9104</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0.8991</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>0.6885</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>0.6747</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>RESNET101</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0.8525</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0.8348</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0.8587</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0.8927</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0.9258999999999999</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0.8993</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>0.6899</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>0.6953</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>RESNET50</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>84.91</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>82.22</v>
+      <c r="B8" s="6" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>0.8491</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>0.8222</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>0.8316</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0.8778</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>0.9206</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0.9059</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>0.7069</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>0.6749000000000001</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/luaran/laporan_akhir/tables/Table6_md_2019_stages.xlsx
+++ b/luaran/laporan_akhir/tables/Table6_md_2019_stages.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -91,7 +90,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -100,7 +99,7 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>

--- a/luaran/laporan_akhir/tables/Table6_md_2019_stages.xlsx
+++ b/luaran/laporan_akhir/tables/Table6_md_2019_stages.xlsx
@@ -578,28 +578,28 @@
         <v>16</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.8353</v>
+        <v>83.53</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.8254</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.8548</v>
+        <v>85.48</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.8933</v>
+        <v>89.33</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.9225</v>
+        <v>92.25</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.875</v>
+        <v>87.5</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.6475</v>
+        <v>64.75</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.6767</v>
+        <v>67.67</v>
       </c>
     </row>
     <row r="4">
@@ -615,28 +615,28 @@
         <v>8.300000000000001</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>0.8662</v>
+        <v>86.61999999999999</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>0.8551</v>
+        <v>85.50999999999999</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>0.8641</v>
+        <v>86.41</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.8983</v>
+        <v>89.83</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.9434</v>
+        <v>94.34</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.9074</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>0.7164</v>
+        <v>71.64</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>0.7356</v>
+        <v>73.56</v>
       </c>
     </row>
     <row r="5">
@@ -652,28 +652,28 @@
         <v>11.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.8559</v>
+        <v>85.59</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.8391</v>
+        <v>83.91</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.8757</v>
+        <v>87.57000000000001</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.8934</v>
+        <v>89.34</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.9265</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.9032</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.6866</v>
+        <v>68.66</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.705</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="6">
@@ -689,28 +689,28 @@
         <v>11.7</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0.8405</v>
+        <v>84.05</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>0.8145</v>
+        <v>81.45</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0.8352000000000001</v>
+        <v>83.52000000000001</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>0.8636</v>
+        <v>86.36</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>0.9104</v>
+        <v>91.03999999999999</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.8991</v>
+        <v>89.91</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>0.6885</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.6747</v>
+        <v>67.47</v>
       </c>
     </row>
     <row r="7">
@@ -726,28 +726,28 @@
         <v>15.6</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.8525</v>
+        <v>85.25</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.8348</v>
+        <v>83.48</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.8587</v>
+        <v>85.87</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.8927</v>
+        <v>89.27000000000001</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.9258999999999999</v>
+        <v>92.58999999999999</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.8993</v>
+        <v>89.92999999999999</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.6899</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.6953</v>
+        <v>69.53</v>
       </c>
     </row>
     <row r="8">
@@ -763,28 +763,28 @@
         <v>11.1</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0.8491</v>
+        <v>84.91</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>0.8222</v>
+        <v>82.22</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>0.8316</v>
+        <v>83.16</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.8778</v>
+        <v>87.78</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.9206</v>
+        <v>92.06</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.9059</v>
+        <v>90.59</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>0.7069</v>
+        <v>70.69</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.6749000000000001</v>
+        <v>67.49000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/luaran/laporan_akhir/tables/Table6_md_2019_stages.xlsx
+++ b/luaran/laporan_akhir/tables/Table6_md_2019_stages.xlsx
@@ -788,10 +788,15 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="8">
+    <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
